--- a/public/templates/po-template.xlsx
+++ b/public/templates/po-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BrandonCode\pck-ledger\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BrandonsLaptop/PCKLedger/ledger-app/public/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EA05EC-CA02-4E29-BDC3-939360BFCE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A09C32-236D-1B4A-8CB7-77061F920A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
+    <workbookView xWindow="400" yWindow="780" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-421]* #,##0.00_-;\-[$Rp-421]* #,##0.00_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,12 +180,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -196,17 +190,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans&quot;"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -220,19 +203,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="2"/>
@@ -252,7 +222,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,12 +233,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF548135"/>
         <bgColor rgb="FF548135"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -284,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -351,110 +315,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD8D8D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD8D8D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD8D8D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FFD8D8D8"/>
@@ -511,19 +371,6 @@
       <bottom style="thin">
         <color rgb="FFD8D8D8"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD8D8D8"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -693,15 +540,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -719,219 +559,146 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1317,515 +1084,534 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF50BD6-2575-46D9-9806-0FE31BACBE95}">
   <dimension ref="B2:H51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
+    <row r="2" spans="2:8" ht="37">
+      <c r="B2" s="59"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="3" spans="2:8">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="7" t="s">
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7" t="s">
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="F9" s="13" t="s">
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="F9" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="19"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="20"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="22"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="26"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="21"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="21"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="21"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="21"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="21"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="2:8">
+      <c r="B15" s="15"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31" t="s">
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="73"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="82"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="74"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="83"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="74"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="83"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="75"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="83"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="83"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="33"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="84"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="33"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="40"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="41"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
+    <row r="18" spans="2:8">
+      <c r="B18" s="21"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="21"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="21"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="21"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="21"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="21"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="21"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="21"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="21"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="33"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
+      <c r="C27" s="46"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="20"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="43"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="33"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
+      <c r="C28" s="46"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="20"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="33"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="42" t="s">
+      <c r="C29" s="46"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="43"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="33"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="45"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="47" t="s">
+      <c r="C30" s="46"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="20"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="48" t="s">
+      <c r="G31" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="49">
+      <c r="H31" s="26">
         <f>H18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="s">
+    <row r="32" spans="2:8">
+      <c r="B32" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="54">
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="28">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="55"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="57">
+    <row r="33" spans="2:8">
+      <c r="B33" s="35"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="55"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="57">
+    <row r="34" spans="2:8">
+      <c r="B34" s="35"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="60"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="57">
+    <row r="35" spans="2:8">
+      <c r="B35" s="37"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="55"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="64" t="s">
+    <row r="36" spans="2:8">
+      <c r="B36" s="35"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="65">
+      <c r="H36" s="32">
         <f>H31-H35</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="60"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="27"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="66"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="27"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="27"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="27"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="70" t="s">
+    <row r="37" spans="2:8">
+      <c r="B37" s="37"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="16"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="16"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="16"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="16"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="27"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43" s="69"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="27"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="27"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="69"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="27"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="69"/>
-      <c r="C46" s="69"/>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="27"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F47" s="27"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="72" t="s">
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="16"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="16"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="16"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="16"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="16"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="F47" s="16"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="F48" s="70" t="s">
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="F48" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="5"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="5"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="33"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34"/>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="33"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="C18:E18"/>
@@ -1842,25 +1628,6 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{AEF25034-3454-4087-856B-CA44CE681A7D}"/>

--- a/public/templates/po-template.xlsx
+++ b/public/templates/po-template.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BrandonsLaptop/PCKLedger/ledger-app/public/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BrandonCode\pck-ledger\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A09C32-236D-1B4A-8CB7-77061F920A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A036D9-CFF7-4C36-9412-CC0334C51D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="780" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$B$2:$H$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -125,7 +128,7 @@
     <numFmt numFmtId="164" formatCode="dd\-mmmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-421]* #,##0.00_-;\-[$Rp-421]* #,##0.00_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,14 +633,42 @@
     <xf numFmtId="165" fontId="14" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -646,6 +677,9 @@
     </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -659,11 +693,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -673,32 +702,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1083,71 +1086,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF50BD6-2575-46D9-9806-0FE31BACBE95}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="37">
-      <c r="B2" s="59"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="60" t="s">
+    <row r="2" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-    </row>
-    <row r="3" spans="2:8">
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="2:8">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,7 +1166,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -1169,7 +1175,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -1178,19 +1184,19 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="62" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="F9" s="62" t="s">
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="F9" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-    </row>
-    <row r="10" spans="2:8">
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="21"/>
       <c r="C10" s="9"/>
       <c r="D10" s="3"/>
@@ -1199,7 +1205,7 @@
       <c r="G10" s="11"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="2:8">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="21"/>
       <c r="C11" s="9"/>
       <c r="D11" s="3"/>
@@ -1208,7 +1214,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="21"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -1217,7 +1223,7 @@
       <c r="G12" s="12"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="21"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1226,7 +1232,7 @@
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="21"/>
       <c r="C14" s="13"/>
       <c r="D14" s="3"/>
@@ -1235,7 +1241,7 @@
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" spans="2:8">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="13"/>
       <c r="D15" s="3"/>
@@ -1244,7 +1250,7 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
@@ -1253,15 +1259,15 @@
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
       <c r="F17" s="18" t="s">
         <v>15</v>
       </c>
@@ -1272,136 +1278,136 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="21"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="48"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="37"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="21"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="48"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="21"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="48"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="37"/>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="21"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="48"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="20"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="21"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="21"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="37"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="21"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="48"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="37"/>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="21"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="48"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="37"/>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="21"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="48"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="48"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="20"/>
       <c r="G27" s="23"/>
       <c r="H27" s="20"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="37"/>
       <c r="F28" s="20"/>
       <c r="G28" s="23"/>
       <c r="H28" s="20"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="48"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="37"/>
       <c r="F29" s="20"/>
       <c r="G29" s="23"/>
       <c r="H29" s="20"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="48"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="20"/>
       <c r="G30" s="23"/>
       <c r="H30" s="20"/>
     </row>
-    <row r="31" spans="2:8">
-      <c r="B31" s="49"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="59"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="24" t="s">
         <v>19</v>
       </c>
@@ -1413,57 +1419,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="51" t="s">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="53"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="63"/>
       <c r="F32" s="27"/>
       <c r="G32" s="25"/>
       <c r="H32" s="28">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
-      <c r="B33" s="35"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="36"/>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="45"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="46"/>
       <c r="F33" s="16"/>
       <c r="G33" s="25"/>
       <c r="H33" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="B34" s="35"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="55"/>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="45"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="48"/>
       <c r="F34" s="16"/>
       <c r="G34" s="25"/>
       <c r="H34" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
-      <c r="B35" s="37"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="49"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="51"/>
       <c r="F35" s="16"/>
       <c r="G35" s="30"/>
       <c r="H35" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
-      <c r="B36" s="35"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="36"/>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="45"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="46"/>
       <c r="F36" s="16"/>
       <c r="G36" s="31" t="s">
         <v>17</v>
@@ -1473,98 +1479,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
-      <c r="B37" s="37"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="49"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="51"/>
       <c r="F37" s="16"/>
     </row>
-    <row r="38" spans="2:8">
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="42"/>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="53"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="55"/>
       <c r="F38" s="16"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="16"/>
     </row>
-    <row r="41" spans="2:8">
-      <c r="B41" s="43" t="s">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-    </row>
-    <row r="42" spans="2:8">
+      <c r="F41" s="56"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="16"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="16"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="16"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="16"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="16"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F47" s="16"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="45" t="s">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="F48" s="43" t="s">
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="F48" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-    </row>
-    <row r="49" spans="2:8">
+      <c r="G48" s="39"/>
+      <c r="H48" s="39"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -1573,45 +1579,26 @@
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="33"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34"/>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="33"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="41"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="41"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="C18:E18"/>
@@ -1628,11 +1615,31 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{AEF25034-3454-4087-856B-CA44CE681A7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <pageSetup scale="77" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/public/templates/po-template.xlsx
+++ b/public/templates/po-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BrandonCode\pck-ledger\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A036D9-CFF7-4C36-9412-CC0334C51D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8807C70F-56CA-428A-902E-8653B7C41CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
+    <workbookView xWindow="1950" yWindow="600" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -123,10 +123,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="dd\-mmmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-421]* #,##0.00_-;\-[$Rp-421]* #,##0.00_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -213,14 +214,15 @@
       <name val="Trebuchet MS"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -543,7 +545,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -597,15 +599,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -630,45 +623,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -678,21 +645,21 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -702,6 +669,47 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1100,25 +1108,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="38"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="40" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4" t="s">
         <v>3</v>
@@ -1129,11 +1137,11 @@
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
         <v>6</v>
@@ -1144,11 +1152,11 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7"/>
       <c r="H5" s="3"/>
@@ -1185,19 +1193,19 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="F9" s="43" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="F9" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="21"/>
+      <c r="B10" s="60"/>
       <c r="C10" s="9"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1206,7 +1214,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
+      <c r="B11" s="60"/>
       <c r="C11" s="9"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -1215,7 +1223,7 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="21"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1224,7 +1232,7 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="21"/>
+      <c r="B13" s="60"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="10"/>
@@ -1233,7 +1241,7 @@
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="21"/>
+      <c r="B14" s="60"/>
       <c r="C14" s="13"/>
       <c r="D14" s="3"/>
       <c r="E14" s="10"/>
@@ -1263,11 +1271,11 @@
       <c r="B17" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
       <c r="F17" s="18" t="s">
         <v>15</v>
       </c>
@@ -1279,218 +1287,218 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="21"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="21"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="37"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="21"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="37"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="21"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="37"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="21"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="21"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="37"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="21"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="37"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="21"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="37"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
       <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="21"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="37"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="37"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="20"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="20"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="62"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="22" t="s">
+      <c r="B28" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="37"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
       <c r="F28" s="20"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="20"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="62"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="37"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="33"/>
       <c r="F29" s="20"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="20"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="62"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="37"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="33"/>
       <c r="F30" s="20"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="20"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="62"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
-      <c r="F31" s="24" t="s">
+      <c r="B31" s="46"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="23">
         <f>H18</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="28">
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="45"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="46"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="35"/>
       <c r="F33" s="16"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="29">
+      <c r="G33" s="22"/>
+      <c r="H33" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="45"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="48"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="52"/>
       <c r="F34" s="16"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="29">
+      <c r="G34" s="22"/>
+      <c r="H34" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="49"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="51"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="38"/>
       <c r="F35" s="16"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="29">
+      <c r="G35" s="27"/>
+      <c r="H35" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="45"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="46"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="35"/>
       <c r="F36" s="16"/>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="65">
         <f>H31-H35</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="49"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="38"/>
       <c r="F37" s="16"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="53"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="41"/>
       <c r="F38" s="16"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
@@ -1508,15 +1516,15 @@
       <c r="F40" s="16"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="56" t="s">
+      <c r="B41" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
@@ -1559,16 +1567,16 @@
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="58" t="s">
+      <c r="B48" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="F48" s="56" t="s">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="F48" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="G48" s="39"/>
-      <c r="H48" s="39"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
@@ -1580,25 +1588,44 @@
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="41"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="39"/>
-      <c r="G50" s="39"/>
-      <c r="H50" s="39"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="41"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="39"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="C18:E18"/>
@@ -1615,25 +1642,6 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{AEF25034-3454-4087-856B-CA44CE681A7D}"/>

--- a/public/templates/po-template.xlsx
+++ b/public/templates/po-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BrandonCode\pck-ledger\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8807C70F-56CA-428A-902E-8653B7C41CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631814E9-4708-4BFB-9BD2-B1296BD82329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="600" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
+    <workbookView xWindow="1170" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
     <t>(Richard Edwin Giovani)</t>
   </si>
   <si>
-    <t>(.....................................)</t>
+    <t>()</t>
   </si>
 </sst>
 </file>
@@ -127,9 +127,9 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="dd\-mmmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$Rp-421]* #,##0.00_-;\-[$Rp-421]* #,##0.00_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,12 +182,6 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -545,7 +539,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -570,12 +564,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -583,7 +571,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -599,7 +586,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -608,35 +595,73 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -645,70 +670,38 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1108,25 +1101,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="55"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="56" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4" t="s">
         <v>3</v>
@@ -1137,11 +1130,11 @@
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
         <v>6</v>
@@ -1152,11 +1145,11 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7"/>
       <c r="H5" s="3"/>
@@ -1193,390 +1186,390 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="F9" s="58" t="s">
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="F9" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="60"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="3"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="60"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="60"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="3"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="60"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="60"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
-      <c r="C15" s="13"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="18" t="s">
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="61"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="61"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="61"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="61"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="61"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="61"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="61"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="61"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="61"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="62"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="62"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="62"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="62"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="27"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="21" t="s">
+      <c r="B31" s="57"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="20">
         <f>H18</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="25">
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="34"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="26">
+      <c r="B33" s="43"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="34"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="26">
+      <c r="B34" s="43"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="36"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="26">
+      <c r="B35" s="47"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="34"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="28" t="s">
+      <c r="B36" s="43"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="H36" s="65">
+      <c r="H36" s="30">
         <f>H31-H35</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="16"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="13"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="39"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="16"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="13"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="16"/>
+      <c r="F39" s="13"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="16"/>
+      <c r="F40" s="13"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="42" t="s">
+      <c r="B41" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="16"/>
+      <c r="F42" s="13"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="16"/>
+      <c r="F43" s="13"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="16"/>
+      <c r="F44" s="13"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="16"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="16"/>
+      <c r="F46" s="13"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="F47" s="16"/>
+      <c r="F47" s="13"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="44" t="s">
+      <c r="B48" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="F48" s="42" t="s">
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="F48" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
@@ -1588,44 +1581,29 @@
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="29"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="29"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
+  <mergeCells count="45">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="C18:E18"/>
@@ -1642,6 +1620,31 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="F14:H14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{AEF25034-3454-4087-856B-CA44CE681A7D}"/>

--- a/public/templates/po-template.xlsx
+++ b/public/templates/po-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BrandonCode\pck-ledger\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631814E9-4708-4BFB-9BD2-B1296BD82329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD2B76C-7BA1-4A11-B14D-C9E7BCBD73AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="14400" windowHeight="15600" xr2:uid="{5E6773E2-7222-400F-9EEC-259D3A26E748}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
     <t>(Richard Edwin Giovani)</t>
   </si>
   <si>
-    <t>()</t>
+    <t>(…..........................................)</t>
   </si>
 </sst>
 </file>
@@ -247,7 +247,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -534,12 +534,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA5A5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA5A5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA5A5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -625,59 +656,18 @@
     <xf numFmtId="165" fontId="14" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -685,6 +675,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -694,14 +687,55 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1101,25 +1135,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
       <c r="F3" s="3"/>
       <c r="G3" s="4" t="s">
         <v>3</v>
@@ -1130,11 +1164,11 @@
       <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="3"/>
       <c r="G4" s="4" t="s">
         <v>6</v>
@@ -1145,11 +1179,11 @@
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="3"/>
       <c r="G5" s="7"/>
       <c r="H5" s="3"/>
@@ -1186,61 +1220,61 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="F9" s="41" t="s">
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="F9" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="12"/>
@@ -1264,11 +1298,11 @@
       <c r="B17" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
       <c r="F17" s="15" t="s">
         <v>15</v>
       </c>
@@ -1364,7 +1398,7 @@
       <c r="B27" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="50"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="34"/>
       <c r="E27" s="35"/>
       <c r="F27" s="17"/>
@@ -1375,7 +1409,7 @@
       <c r="B28" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="50"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="34"/>
       <c r="E28" s="35"/>
       <c r="F28" s="17"/>
@@ -1386,7 +1420,7 @@
       <c r="B29" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="50"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="34"/>
       <c r="E29" s="35"/>
       <c r="F29" s="17"/>
@@ -1397,7 +1431,7 @@
       <c r="B30" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="50"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="34"/>
       <c r="E30" s="35"/>
       <c r="F30" s="17"/>
@@ -1405,10 +1439,10 @@
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
       <c r="F31" s="18" t="s">
         <v>19</v>
       </c>
@@ -1421,12 +1455,12 @@
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="61"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="45"/>
       <c r="F32" s="21"/>
       <c r="G32" s="19"/>
       <c r="H32" s="22">
@@ -1434,10 +1468,10 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="43"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="44"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="56"/>
       <c r="F33" s="13"/>
       <c r="G33" s="19"/>
       <c r="H33" s="23">
@@ -1445,9 +1479,9 @@
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="43"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
       <c r="E34" s="46"/>
       <c r="F34" s="13"/>
       <c r="G34" s="19"/>
@@ -1456,10 +1490,10 @@
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="47"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="49"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="46"/>
       <c r="F35" s="13"/>
       <c r="G35" s="24"/>
       <c r="H35" s="23">
@@ -1467,10 +1501,10 @@
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="43"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="44"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="46"/>
       <c r="F36" s="13"/>
       <c r="G36" s="25" t="s">
         <v>17</v>
@@ -1481,17 +1515,17 @@
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="47"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="49"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="46"/>
       <c r="F37" s="13"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="53"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="60"/>
       <c r="F38" s="13"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
@@ -1509,15 +1543,15 @@
       <c r="F40" s="13"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
@@ -1560,16 +1594,16 @@
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B48" s="56" t="s">
+      <c r="B48" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="F48" s="54" t="s">
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="F48" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="3"/>
@@ -1581,38 +1615,44 @@
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="39"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="39"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="37"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B50:H50"/>
+  <mergeCells count="36">
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B33:E38"/>
+    <mergeCell ref="B10:D14"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="B48:D48"/>
@@ -1620,9 +1660,7 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B50:H50"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
@@ -1632,19 +1670,6 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F14:H14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C6" r:id="rId1" xr:uid="{AEF25034-3454-4087-856B-CA44CE681A7D}"/>
